--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R2" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R4" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B6" t="n">
-        <v>56425</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R6" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,38 +1220,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>56425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R7" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1306,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130664986</v>
+        <v>130661851</v>
       </c>
       <c r="B8" t="n">
         <v>79209</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491418</v>
+        <v>491476</v>
       </c>
       <c r="R8" t="n">
-        <v>6759396</v>
+        <v>6759437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130661851</v>
+        <v>130671725</v>
       </c>
       <c r="B9" t="n">
         <v>79209</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491476</v>
+        <v>491530</v>
       </c>
       <c r="R9" t="n">
-        <v>6759437</v>
+        <v>6759308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130671725</v>
+        <v>130664986</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491530</v>
+        <v>491418</v>
       </c>
       <c r="R10" t="n">
-        <v>6759308</v>
+        <v>6759396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130661581</v>
+        <v>130661613</v>
       </c>
       <c r="B20" t="n">
         <v>79209</v>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491481</v>
+        <v>491477</v>
       </c>
       <c r="R20" t="n">
-        <v>6759380</v>
+        <v>6759416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661613</v>
+        <v>130661581</v>
       </c>
       <c r="B21" t="n">
         <v>79209</v>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491477</v>
+        <v>491481</v>
       </c>
       <c r="R21" t="n">
-        <v>6759416</v>
+        <v>6759380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,50 +2977,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130668332</v>
+        <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491384</v>
+        <v>491430</v>
       </c>
       <c r="R23" t="n">
-        <v>6759354</v>
+        <v>6759427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,45 +3084,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130664348</v>
+        <v>130668332</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R24" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3632,6 +3632,126 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130669116</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57852</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brunnvasselån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>491360</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6759395</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>5 hackål/bohål, 4 till 6 cm i diameter, ca 4 meter upp. Tretåig hackspett har sannolikt nyttjat det nedre bohålet.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130661609</v>
+        <v>130670771</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491477</v>
+        <v>491374</v>
       </c>
       <c r="R2" t="n">
         <v>6759416</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670771</v>
+        <v>130670627</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491374</v>
+        <v>491376</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670627</v>
+        <v>130667093</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491376</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6759442</v>
+        <v>6759381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130667093</v>
+        <v>130661609</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491408</v>
+        <v>491477</v>
       </c>
       <c r="R5" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>56427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R6" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1194,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,38 +1225,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B7" t="n">
-        <v>56425</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R7" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1311,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1340,7 @@
         <v>130661851</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130671725</v>
+        <v>130664986</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491530</v>
+        <v>491418</v>
       </c>
       <c r="R9" t="n">
-        <v>6759308</v>
+        <v>6759396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130664986</v>
+        <v>130671725</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491418</v>
+        <v>491530</v>
       </c>
       <c r="R10" t="n">
-        <v>6759396</v>
+        <v>6759308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
         <v>130668644</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>130662909</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130665997</v>
+        <v>130668452</v>
       </c>
       <c r="B14" t="n">
         <v>8451</v>
@@ -2020,7 +2020,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491418</v>
+        <v>491385</v>
       </c>
       <c r="R14" t="n">
-        <v>6759396</v>
+        <v>6759286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130668452</v>
+        <v>130665997</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2132,7 +2132,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491385</v>
+        <v>491418</v>
       </c>
       <c r="R15" t="n">
-        <v>6759286</v>
+        <v>6759396</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>130661510</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>130662331</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>130661613</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>130661581</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>130670281</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>130668710</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,35 +3415,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>56427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3522,40 +3527,35 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B28" t="n">
-        <v>56425</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670771</v>
+        <v>130667093</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491374</v>
+        <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R3" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R4" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R5" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1658,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R11" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,45 +1765,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130668644</v>
+        <v>130662234</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491424</v>
+        <v>491455</v>
       </c>
       <c r="R12" t="n">
-        <v>6759256</v>
+        <v>6759425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2977,45 +2977,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130664348</v>
+        <v>130668332</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R23" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,50 +3089,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130668332</v>
+        <v>130664348</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491384</v>
+        <v>491430</v>
       </c>
       <c r="R24" t="n">
-        <v>6759354</v>
+        <v>6759427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3415,40 +3415,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B27" t="n">
-        <v>56427</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3527,35 +3522,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>56427</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R2" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670771</v>
+        <v>130667093</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491374</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R5" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1658,45 +1658,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130668644</v>
+        <v>130662234</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491424</v>
+        <v>491455</v>
       </c>
       <c r="R11" t="n">
-        <v>6759256</v>
+        <v>6759425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,50 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R12" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130668452</v>
+        <v>130665997</v>
       </c>
       <c r="B14" t="n">
         <v>8451</v>
@@ -2020,7 +2020,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491385</v>
+        <v>491418</v>
       </c>
       <c r="R14" t="n">
-        <v>6759286</v>
+        <v>6759396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130665997</v>
+        <v>130668452</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2132,7 +2132,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491418</v>
+        <v>491385</v>
       </c>
       <c r="R15" t="n">
-        <v>6759396</v>
+        <v>6759286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130661613</v>
+        <v>130670281</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,34 +2662,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491477</v>
+        <v>491315</v>
       </c>
       <c r="R20" t="n">
-        <v>6759416</v>
+        <v>6759520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2763,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661581</v>
+        <v>130661613</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2793,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491481</v>
+        <v>491477</v>
       </c>
       <c r="R21" t="n">
-        <v>6759380</v>
+        <v>6759416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130670281</v>
+        <v>130661581</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,39 +2881,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491315</v>
+        <v>491481</v>
       </c>
       <c r="R22" t="n">
-        <v>6759520</v>
+        <v>6759380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670771</v>
+        <v>130670627</v>
       </c>
       <c r="B2" t="n">
         <v>79211</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491374</v>
+        <v>491376</v>
       </c>
       <c r="R2" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670627</v>
+        <v>130670771</v>
       </c>
       <c r="B3" t="n">
         <v>79211</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491376</v>
+        <v>491374</v>
       </c>
       <c r="R3" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130667093</v>
+        <v>130661609</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491408</v>
+        <v>491477</v>
       </c>
       <c r="R4" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130661609</v>
+        <v>130667093</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491477</v>
+        <v>491408</v>
       </c>
       <c r="R5" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B6" t="n">
-        <v>56427</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R6" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,38 +1220,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>56427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R7" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1306,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130661851</v>
+        <v>130671725</v>
       </c>
       <c r="B8" t="n">
         <v>79211</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491476</v>
+        <v>491530</v>
       </c>
       <c r="R8" t="n">
-        <v>6759437</v>
+        <v>6759308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130671725</v>
+        <v>130661851</v>
       </c>
       <c r="B10" t="n">
         <v>79211</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491530</v>
+        <v>491476</v>
       </c>
       <c r="R10" t="n">
-        <v>6759308</v>
+        <v>6759437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130665997</v>
+        <v>130668452</v>
       </c>
       <c r="B14" t="n">
         <v>8451</v>
@@ -2020,7 +2020,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491418</v>
+        <v>491385</v>
       </c>
       <c r="R14" t="n">
-        <v>6759396</v>
+        <v>6759286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130668452</v>
+        <v>130665997</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2132,7 +2132,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491385</v>
+        <v>491418</v>
       </c>
       <c r="R15" t="n">
-        <v>6759286</v>
+        <v>6759396</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,45 +2213,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R16" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,50 +2325,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R17" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130670281</v>
+        <v>130661613</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,39 +2662,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491315</v>
+        <v>491477</v>
       </c>
       <c r="R20" t="n">
-        <v>6759520</v>
+        <v>6759416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661613</v>
+        <v>130661581</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2798,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491477</v>
+        <v>491481</v>
       </c>
       <c r="R21" t="n">
-        <v>6759416</v>
+        <v>6759380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130661581</v>
+        <v>130670281</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2881,34 +2876,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491481</v>
+        <v>491315</v>
       </c>
       <c r="R22" t="n">
-        <v>6759380</v>
+        <v>6759520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,50 +2977,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130668332</v>
+        <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491384</v>
+        <v>491430</v>
       </c>
       <c r="R23" t="n">
-        <v>6759354</v>
+        <v>6759427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,45 +3084,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130664348</v>
+        <v>130668332</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R24" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670627</v>
+        <v>130667093</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491376</v>
+        <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6759442</v>
+        <v>6759381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R4" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130667093</v>
+        <v>130661609</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491408</v>
+        <v>491477</v>
       </c>
       <c r="R5" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130671725</v>
+        <v>130661851</v>
       </c>
       <c r="B8" t="n">
         <v>79211</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491530</v>
+        <v>491476</v>
       </c>
       <c r="R8" t="n">
-        <v>6759308</v>
+        <v>6759437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130661851</v>
+        <v>130671725</v>
       </c>
       <c r="B10" t="n">
         <v>79211</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491476</v>
+        <v>491530</v>
       </c>
       <c r="R10" t="n">
-        <v>6759437</v>
+        <v>6759308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R11" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,45 +1765,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130668644</v>
+        <v>130662234</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491424</v>
+        <v>491455</v>
       </c>
       <c r="R12" t="n">
-        <v>6759256</v>
+        <v>6759425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130661613</v>
+        <v>130670281</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,34 +2662,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491477</v>
+        <v>491315</v>
       </c>
       <c r="R20" t="n">
-        <v>6759416</v>
+        <v>6759520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2763,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661581</v>
+        <v>130661613</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2793,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491481</v>
+        <v>491477</v>
       </c>
       <c r="R21" t="n">
-        <v>6759380</v>
+        <v>6759416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130670281</v>
+        <v>130661581</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,39 +2881,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491315</v>
+        <v>491481</v>
       </c>
       <c r="R22" t="n">
-        <v>6759520</v>
+        <v>6759380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3415,35 +3415,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>56427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3522,40 +3527,35 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B28" t="n">
-        <v>56427</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130667093</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670771</v>
+        <v>130661609</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491374</v>
+        <v>491477</v>
       </c>
       <c r="R3" t="n">
         <v>6759416</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670627</v>
+        <v>130670771</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491376</v>
+        <v>491374</v>
       </c>
       <c r="R4" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R5" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>56427</v>
+        <v>56435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>130661851</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>130664986</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>130671725</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>130662909</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>130661510</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>130662331</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130670281</v>
+        <v>130661613</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,39 +2662,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491315</v>
+        <v>491477</v>
       </c>
       <c r="R20" t="n">
-        <v>6759520</v>
+        <v>6759416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2763,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661613</v>
+        <v>130661581</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491477</v>
+        <v>491481</v>
       </c>
       <c r="R21" t="n">
-        <v>6759416</v>
+        <v>6759380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130661581</v>
+        <v>130670281</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2881,34 +2876,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491481</v>
+        <v>491315</v>
       </c>
       <c r="R22" t="n">
-        <v>6759380</v>
+        <v>6759520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
         <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>130668710</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,40 +3415,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B27" t="n">
-        <v>56427</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3527,35 +3522,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>56435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R2" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670771</v>
+        <v>130667093</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491374</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R5" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>56435</v>
+        <v>56436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>130661851</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>130664986</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>130671725</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>130662909</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2213,50 +2213,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R16" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,45 +2320,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R17" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
         <v>130662331</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>130661613</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>130661581</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>130670281</v>
       </c>
       <c r="B22" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>130668710</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,35 +3415,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3522,40 +3527,35 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B28" t="n">
-        <v>56435</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670771</v>
+        <v>130670627</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491374</v>
+        <v>491376</v>
       </c>
       <c r="R2" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670627</v>
+        <v>130670771</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491376</v>
+        <v>491374</v>
       </c>
       <c r="R3" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>130667093</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R6" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1194,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,38 +1225,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B7" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R7" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1311,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130661851</v>
+        <v>130664986</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491476</v>
+        <v>491418</v>
       </c>
       <c r="R8" t="n">
-        <v>6759437</v>
+        <v>6759396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130664986</v>
+        <v>130671725</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491418</v>
+        <v>491530</v>
       </c>
       <c r="R9" t="n">
-        <v>6759396</v>
+        <v>6759308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130671725</v>
+        <v>130661851</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491530</v>
+        <v>491476</v>
       </c>
       <c r="R10" t="n">
-        <v>6759308</v>
+        <v>6759437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1661,7 @@
         <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>130662909</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2213,45 +2213,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R16" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,50 +2325,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R17" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
         <v>130662331</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>130661613</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>130661581</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>130670281</v>
       </c>
       <c r="B22" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>130668710</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,40 +3415,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B27" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3527,35 +3522,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670627</v>
+        <v>130667093</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491376</v>
+        <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6759442</v>
+        <v>6759381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670771</v>
+        <v>130670627</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491374</v>
+        <v>491376</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R4" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130664986</v>
+        <v>130671725</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491418</v>
+        <v>491530</v>
       </c>
       <c r="R8" t="n">
-        <v>6759396</v>
+        <v>6759308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130671725</v>
+        <v>130664986</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491530</v>
+        <v>491418</v>
       </c>
       <c r="R9" t="n">
-        <v>6759308</v>
+        <v>6759396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1658,45 +1658,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130668644</v>
+        <v>130662234</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491424</v>
+        <v>491455</v>
       </c>
       <c r="R11" t="n">
-        <v>6759256</v>
+        <v>6759425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,50 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R12" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,38 +1877,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130662909</v>
+        <v>130668452</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491455</v>
+        <v>491385</v>
       </c>
       <c r="R13" t="n">
-        <v>6759425</v>
+        <v>6759286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130668452</v>
+        <v>130665997</v>
       </c>
       <c r="B14" t="n">
         <v>8451</v>
@@ -2020,7 +2020,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491385</v>
+        <v>491418</v>
       </c>
       <c r="R14" t="n">
-        <v>6759286</v>
+        <v>6759396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,38 +2101,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130665997</v>
+        <v>130662909</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491418</v>
+        <v>491455</v>
       </c>
       <c r="R15" t="n">
-        <v>6759396</v>
+        <v>6759425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,50 +2213,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R16" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,45 +2320,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R17" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R2" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670771</v>
+        <v>130661609</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,7 +924,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491374</v>
+        <v>491477</v>
       </c>
       <c r="R4" t="n">
         <v>6759416</v>
@@ -1001,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130661609</v>
+        <v>130667093</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491477</v>
+        <v>491408</v>
       </c>
       <c r="R5" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B6" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R6" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,38 +1220,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R7" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1306,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130671725</v>
+        <v>130661851</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491530</v>
+        <v>491476</v>
       </c>
       <c r="R8" t="n">
-        <v>6759308</v>
+        <v>6759437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130661851</v>
+        <v>130671725</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491476</v>
+        <v>491530</v>
       </c>
       <c r="R10" t="n">
-        <v>6759437</v>
+        <v>6759308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R11" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,45 +1765,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130668644</v>
+        <v>130662234</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491424</v>
+        <v>491455</v>
       </c>
       <c r="R12" t="n">
-        <v>6759256</v>
+        <v>6759425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2213,45 +2213,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R16" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,50 +2325,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R17" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130661613</v>
+        <v>130670281</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,34 +2662,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491477</v>
+        <v>491315</v>
       </c>
       <c r="R20" t="n">
-        <v>6759416</v>
+        <v>6759520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2763,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661581</v>
+        <v>130661613</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2793,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491481</v>
+        <v>491477</v>
       </c>
       <c r="R21" t="n">
-        <v>6759380</v>
+        <v>6759416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130670281</v>
+        <v>130661581</v>
       </c>
       <c r="B22" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,39 +2881,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491315</v>
+        <v>491481</v>
       </c>
       <c r="R22" t="n">
-        <v>6759520</v>
+        <v>6759380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3415,35 +3415,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3522,40 +3527,35 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B28" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130670771</v>
+        <v>130667093</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491374</v>
+        <v>491408</v>
       </c>
       <c r="R2" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R3" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130661609</v>
+        <v>130670771</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,7 +929,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491477</v>
+        <v>491374</v>
       </c>
       <c r="R4" t="n">
         <v>6759416</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130667093</v>
+        <v>130670627</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491408</v>
+        <v>491376</v>
       </c>
       <c r="R5" t="n">
-        <v>6759381</v>
+        <v>6759442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R6" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1194,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,38 +1225,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B7" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R7" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1311,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1989,38 +1989,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130665997</v>
+        <v>130662909</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491418</v>
+        <v>491455</v>
       </c>
       <c r="R14" t="n">
-        <v>6759396</v>
+        <v>6759425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,38 +2101,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130662909</v>
+        <v>130665997</v>
       </c>
       <c r="B15" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491455</v>
+        <v>491418</v>
       </c>
       <c r="R15" t="n">
-        <v>6759425</v>
+        <v>6759396</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2977,45 +2977,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130664348</v>
+        <v>130668332</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R23" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,50 +3089,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130668332</v>
+        <v>130664348</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491384</v>
+        <v>491430</v>
       </c>
       <c r="R24" t="n">
-        <v>6759354</v>
+        <v>6759427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130667093</v>
+        <v>130670771</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491408</v>
+        <v>491374</v>
       </c>
       <c r="R2" t="n">
-        <v>6759381</v>
+        <v>6759416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130661609</v>
+        <v>130670627</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491477</v>
+        <v>491376</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670771</v>
+        <v>130667093</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491374</v>
+        <v>491408</v>
       </c>
       <c r="R4" t="n">
-        <v>6759416</v>
+        <v>6759381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130670627</v>
+        <v>130661609</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R5" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,38 +1108,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130665803</v>
+        <v>130668910</v>
       </c>
       <c r="B6" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491418</v>
+        <v>491405</v>
       </c>
       <c r="R6" t="n">
-        <v>6759396</v>
+        <v>6759326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,38 +1220,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130668910</v>
+        <v>130665803</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491405</v>
+        <v>491418</v>
       </c>
       <c r="R7" t="n">
-        <v>6759326</v>
+        <v>6759396</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1306,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1877,38 +1877,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130668452</v>
+        <v>130662909</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491385</v>
+        <v>491455</v>
       </c>
       <c r="R13" t="n">
-        <v>6759286</v>
+        <v>6759425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,38 +1989,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130662909</v>
+        <v>130665997</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491455</v>
+        <v>491418</v>
       </c>
       <c r="R14" t="n">
-        <v>6759425</v>
+        <v>6759396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130665997</v>
+        <v>130668452</v>
       </c>
       <c r="B15" t="n">
         <v>8451</v>
@@ -2132,7 +2132,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491418</v>
+        <v>491385</v>
       </c>
       <c r="R15" t="n">
-        <v>6759396</v>
+        <v>6759286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,50 +2213,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661548</v>
+        <v>130661510</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491487</v>
+        <v>491504</v>
       </c>
       <c r="R16" t="n">
-        <v>6759357</v>
+        <v>6759336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,45 +2320,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661510</v>
+        <v>130661548</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491504</v>
+        <v>491487</v>
       </c>
       <c r="R17" t="n">
-        <v>6759336</v>
+        <v>6759357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2977,50 +2977,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130668332</v>
+        <v>130664348</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491384</v>
+        <v>491430</v>
       </c>
       <c r="R23" t="n">
-        <v>6759354</v>
+        <v>6759427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,45 +3084,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130664348</v>
+        <v>130668332</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R24" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3415,40 +3415,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663880</v>
+        <v>130663940</v>
       </c>
       <c r="B27" t="n">
-        <v>56436</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
@@ -3527,35 +3522,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663940</v>
+        <v>130663880</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>56436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -3637,7 +3637,7 @@
         <v>130669116</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130661609</v>
+        <v>130661510</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491477</v>
+        <v>491504</v>
       </c>
       <c r="R2" t="n">
-        <v>6759416</v>
+        <v>6759336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130670771</v>
+        <v>130661571</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491374</v>
+        <v>491481</v>
       </c>
       <c r="R3" t="n">
-        <v>6759416</v>
+        <v>6759380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130670627</v>
+        <v>130661613</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491376</v>
+        <v>491477</v>
       </c>
       <c r="R4" t="n">
-        <v>6759442</v>
+        <v>6759416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130667093</v>
+        <v>130661790</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491408</v>
+        <v>491485</v>
       </c>
       <c r="R5" t="n">
-        <v>6759381</v>
+        <v>6759439</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130668910</v>
+        <v>130661851</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491405</v>
+        <v>491476</v>
       </c>
       <c r="R6" t="n">
-        <v>6759326</v>
+        <v>6759437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130665803</v>
+        <v>130662331</v>
       </c>
       <c r="B7" t="n">
-        <v>56456</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491418</v>
+        <v>491455</v>
       </c>
       <c r="R7" t="n">
-        <v>6759396</v>
+        <v>6759425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1291,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår efter skogsharen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130661851</v>
+        <v>130664348</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1372,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491476</v>
+        <v>491430</v>
       </c>
       <c r="R8" t="n">
-        <v>6759437</v>
+        <v>6759427</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,11 +1427,11 @@
         <v>130664986</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1551,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130671725</v>
+        <v>130668497</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1586,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491530</v>
+        <v>491386</v>
       </c>
       <c r="R10" t="n">
-        <v>6759308</v>
+        <v>6759268</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130668644</v>
+        <v>130668511</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1693,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491424</v>
+        <v>491391</v>
       </c>
       <c r="R11" t="n">
-        <v>6759256</v>
+        <v>6759258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,50 +1745,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130662234</v>
+        <v>130668644</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491455</v>
+        <v>491424</v>
       </c>
       <c r="R12" t="n">
-        <v>6759425</v>
+        <v>6759256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,50 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130662909</v>
+        <v>130668701</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491455</v>
+        <v>491419</v>
       </c>
       <c r="R13" t="n">
-        <v>6759425</v>
+        <v>6759284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,50 +1959,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130668452</v>
+        <v>130670627</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491385</v>
+        <v>491376</v>
       </c>
       <c r="R14" t="n">
-        <v>6759286</v>
+        <v>6759442</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130665997</v>
+        <v>130670771</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491418</v>
+        <v>491374</v>
       </c>
       <c r="R15" t="n">
-        <v>6759396</v>
+        <v>6759416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130661510</v>
+        <v>130671725</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2248,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491504</v>
+        <v>491530</v>
       </c>
       <c r="R16" t="n">
-        <v>6759336</v>
+        <v>6759308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130661548</v>
+        <v>130662909</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,27 +2291,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2360,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491487</v>
+        <v>491455</v>
       </c>
       <c r="R17" t="n">
-        <v>6759357</v>
+        <v>6759425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130662331</v>
+        <v>130667093</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,34 +2403,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491455</v>
+        <v>491408</v>
       </c>
       <c r="R18" t="n">
-        <v>6759425</v>
+        <v>6759381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,50 +2504,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130661580</v>
+        <v>130669116</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491481</v>
+        <v>491360</v>
       </c>
       <c r="R19" t="n">
-        <v>6759380</v>
+        <v>6759395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,11 +2595,16 @@
           <t>10:06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 hackål/bohål, 4 till 6 cm i diameter, ca 4 meter upp. Tretåig hackspett har sannolikt nyttjat det nedre bohålet.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2651,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130661613</v>
+        <v>130670281</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,34 +2635,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491477</v>
+        <v>491315</v>
       </c>
       <c r="R20" t="n">
-        <v>6759416</v>
+        <v>6759520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,45 +2736,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130661581</v>
+        <v>130661548</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491481</v>
+        <v>491487</v>
       </c>
       <c r="R21" t="n">
-        <v>6759380</v>
+        <v>6759357</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,38 +2848,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130670281</v>
+        <v>130661580</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2905,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491315</v>
+        <v>491481</v>
       </c>
       <c r="R22" t="n">
-        <v>6759520</v>
+        <v>6759380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130668332</v>
+        <v>130661609</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,21 +2989,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491384</v>
+        <v>491477</v>
       </c>
       <c r="R23" t="n">
-        <v>6759354</v>
+        <v>6759416</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,45 +3067,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130664348</v>
+        <v>130662234</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491430</v>
+        <v>491455</v>
       </c>
       <c r="R24" t="n">
-        <v>6759427</v>
+        <v>6759425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3196,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130668169</v>
+        <v>130663940</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3225,21 +3208,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491385</v>
+        <v>491430</v>
       </c>
       <c r="R25" t="n">
-        <v>6759389</v>
+        <v>6759427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,45 +3286,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130668710</v>
+        <v>130664935</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491419</v>
+        <v>491418</v>
       </c>
       <c r="R26" t="n">
-        <v>6759284</v>
+        <v>6759396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,38 +3398,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130663880</v>
+        <v>130668169</v>
       </c>
       <c r="B27" t="n">
-        <v>56456</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3455,10 +3438,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491430</v>
+        <v>491385</v>
       </c>
       <c r="R27" t="n">
-        <v>6759427</v>
+        <v>6759389</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3527,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130663940</v>
+        <v>130668332</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,16 +3539,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491430</v>
+        <v>491384</v>
       </c>
       <c r="R28" t="n">
-        <v>6759427</v>
+        <v>6759354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,53 +3622,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130669116</v>
+        <v>130668452</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Brunnvasselån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491360</v>
+        <v>491385</v>
       </c>
       <c r="R29" t="n">
-        <v>6759395</v>
+        <v>6759286</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3725,16 +3710,11 @@
           <t>10:06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>5 hackål/bohål, 4 till 6 cm i diameter, ca 4 meter upp. Tretåig hackspett har sannolikt nyttjat det nedre bohålet.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3751,6 +3731,347 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130668910</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brunnvasselån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>491405</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6759326</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130663880</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brunnvasselån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>491430</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6759427</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130665803</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brunnvasselån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>491418</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6759396</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med spår efter skogsharen</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58478-2025 artfynd.xlsx
+++ b/artfynd/A 58478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661571</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661851</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130662331</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130664348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130664986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668497</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668511</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668701</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130670627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130670771</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130671725</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130662909</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130667093</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669116</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2733,6 +2828,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130670281</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2845,6 +2945,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661548</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2957,6 +3062,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661580</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3064,6 +3174,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130661609</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3176,6 +3291,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130662234</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3283,6 +3403,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130663940</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3395,6 +3520,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130664935</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3507,6 +3637,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668169</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3619,6 +3754,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668332</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3731,6 +3871,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668452</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3843,6 +3988,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130668910</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3955,6 +4105,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130663880</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4072,8 +4227,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130665803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>